--- a/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/For Winter Ending (Actual)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45969</v>
+        <v>45983</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45985</v>
+        <v>45990</v>
       </c>
       <c r="C4" s="2">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45988</v>
+        <v>45992</v>
       </c>
       <c r="C5" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45991</v>
+        <v>45993</v>
       </c>
       <c r="C6" s="2">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="C8" s="2">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45997</v>
+        <v>46000</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>322</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>7</v>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="C10" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45998</v>
+        <v>46003</v>
       </c>
       <c r="C11" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +574,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45998</v>
+        <v>46004</v>
       </c>
       <c r="C12" s="2">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45999</v>
+        <v>46005</v>
       </c>
       <c r="C13" s="2">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46001</v>
+        <v>46005</v>
       </c>
       <c r="C14" s="2">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C15" s="2">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>382</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46004</v>
+        <v>46007</v>
       </c>
       <c r="C17" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46005</v>
+        <v>46008</v>
       </c>
       <c r="C18" s="2">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46005</v>
+        <v>46008</v>
       </c>
       <c r="C19" s="2">
-        <v>926</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C20" s="2">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C21" s="2">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46008</v>
+        <v>46012</v>
       </c>
       <c r="C22" s="2">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46010</v>
+        <v>46012</v>
       </c>
       <c r="C23" s="2">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C24" s="2">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46011</v>
+        <v>46015</v>
       </c>
       <c r="C25" s="2">
-        <v>1006</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46012</v>
+        <v>46015</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46013</v>
+        <v>46017</v>
       </c>
       <c r="C27" s="2">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>7</v>
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="C28" s="2">
-        <v>767</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>7</v>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="C29" s="2">
-        <v>1313</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46015</v>
+        <v>46019</v>
       </c>
       <c r="C30" s="2">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="C32" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>7</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c r="C33" s="2">
-        <v>1018</v>
+        <v>493</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>6</v>
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46018</v>
+        <v>46022</v>
       </c>
       <c r="C34" s="2">
-        <v>2</v>
+        <v>2030</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,10 +896,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46020</v>
+        <v>46023</v>
       </c>
       <c r="C35" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>7</v>
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46020</v>
+        <v>46024</v>
       </c>
       <c r="C36" s="2">
-        <v>2046</v>
+        <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C37" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C38" s="2">
-        <v>1552</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C40" s="2">
-        <v>9</v>
+        <v>1099</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C41" s="2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>7</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C42" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>7</v>
@@ -1008,10 +1008,10 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C43" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>7</v>
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C44" s="2">
-        <v>322</v>
+        <v>1411</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="C45" s="2">
-        <v>97</v>
+        <v>460</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>7</v>
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>7</v>
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="C47" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>7</v>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="C48" s="2">
         <v>2</v>
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="C49" s="2">
-        <v>7</v>
+        <v>836</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="C50" s="2">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,7 +1123,7 @@
         <v>46031</v>
       </c>
       <c r="C51" s="2">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>7</v>
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46033</v>
+        <v>46032</v>
       </c>
       <c r="C52" s="2">
-        <v>30</v>
+        <v>2029</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46033</v>
+        <v>45983</v>
       </c>
       <c r="C53" s="2">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45984</v>
+        <v>45986</v>
       </c>
       <c r="C54" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="C55" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>45989</v>
       </c>
       <c r="C56" s="2">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>7</v>
@@ -1207,10 +1207,10 @@
         <v>45990</v>
       </c>
       <c r="C57" s="2">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45991</v>
+        <v>45990</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>7</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C59" s="2">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>7</v>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45998</v>
+        <v>45992</v>
       </c>
       <c r="C60" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>7</v>
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46000</v>
+        <v>45993</v>
       </c>
       <c r="C61" s="2">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>46001</v>
+        <v>45993</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>7</v>
@@ -1288,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>46001</v>
+        <v>45994</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>7</v>
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>46002</v>
+        <v>45995</v>
       </c>
       <c r="C64" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c r="C65" s="2">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46003</v>
+        <v>45997</v>
       </c>
       <c r="C66" s="2">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>7</v>
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46004</v>
+        <v>45999</v>
       </c>
       <c r="C67" s="2">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1361,7 +1361,7 @@
         <v>46005</v>
       </c>
       <c r="C68" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>7</v>
@@ -1375,10 +1375,10 @@
         <v>46005</v>
       </c>
       <c r="C69" s="2">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C70" s="2">
-        <v>54</v>
+        <v>356</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C71" s="2">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>7</v>
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C72" s="2">
-        <v>46</v>
+        <v>489</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1428,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>46008</v>
+        <v>46011</v>
       </c>
       <c r="C73" s="2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>46009</v>
+        <v>46012</v>
       </c>
       <c r="C74" s="2">
-        <v>82</v>
+        <v>1040</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C75" s="2">
-        <v>345</v>
+        <v>673</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>7</v>
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C76" s="2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>7</v>
@@ -1484,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C77" s="2">
-        <v>533</v>
+        <v>6</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>46011</v>
+        <v>46014</v>
       </c>
       <c r="C78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>46012</v>
+        <v>46015</v>
       </c>
       <c r="C79" s="2">
-        <v>883</v>
+        <v>1186</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>46012</v>
+        <v>46015</v>
       </c>
       <c r="C80" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>7</v>
@@ -1540,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>46013</v>
+        <v>46016</v>
       </c>
       <c r="C81" s="2">
-        <v>1279</v>
+        <v>499</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="C83" s="2">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>46015</v>
+        <v>46019</v>
       </c>
       <c r="C84" s="2">
-        <v>604</v>
+        <v>465</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>46016</v>
+        <v>46019</v>
       </c>
       <c r="C85" s="2">
-        <v>1035</v>
+        <v>777</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>46018</v>
+        <v>46020</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>7</v>
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>46018</v>
+        <v>46021</v>
       </c>
       <c r="C87" s="2">
-        <v>567</v>
+        <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>7</v>
@@ -1638,13 +1638,13 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>46019</v>
+        <v>46021</v>
       </c>
       <c r="C88" s="2">
-        <v>1514</v>
+        <v>51</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="C89" s="2">
-        <v>1</v>
+        <v>607</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>46023</v>
+        <v>46022</v>
       </c>
       <c r="C90" s="2">
-        <v>4</v>
+        <v>588</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>7</v>
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C91" s="2">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>7</v>
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C92" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>7</v>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C93" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>7</v>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C94" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>7</v>
@@ -1736,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>46028</v>
+        <v>46024</v>
       </c>
       <c r="C95" s="2">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>7</v>
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>46030</v>
+        <v>46025</v>
       </c>
       <c r="C96" s="2">
-        <v>6</v>
+        <v>406</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,13 +1764,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>46030</v>
+        <v>46025</v>
       </c>
       <c r="C97" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1778,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>46031</v>
+        <v>46025</v>
       </c>
       <c r="C98" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>7</v>
@@ -1792,13 +1792,13 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="C99" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C100" s="2">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>7</v>
@@ -1820,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>46033</v>
+        <v>46028</v>
       </c>
       <c r="C101" s="2">
-        <v>4</v>
+        <v>258</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,10 +1834,10 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C102" s="2">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>7</v>
@@ -1848,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C103" s="2">
         <v>7</v>
@@ -1862,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C104" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1876,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>45983</v>
+        <v>46032</v>
       </c>
       <c r="C105" s="2">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>6</v>
@@ -1890,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>45986</v>
+        <v>45984</v>
       </c>
       <c r="C106" s="2">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,13 +1904,13 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="C107" s="2">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>45989</v>
       </c>
       <c r="C108" s="2">
-        <v>8</v>
+        <v>335</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -1935,10 +1935,10 @@
         <v>45990</v>
       </c>
       <c r="C109" s="2">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1946,10 +1946,10 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>45990</v>
+        <v>45991</v>
       </c>
       <c r="C110" s="2">
-        <v>263</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>7</v>
@@ -1960,10 +1960,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>45991</v>
+        <v>45998</v>
       </c>
       <c r="C111" s="2">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>7</v>
@@ -1974,10 +1974,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>45992</v>
+        <v>45998</v>
       </c>
       <c r="C112" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>7</v>
@@ -1988,13 +1988,13 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="C113" s="2">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,10 +2002,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="C114" s="2">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>7</v>
@@ -2016,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="C115" s="2">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>7</v>
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="2">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="C116" s="2">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,13 +2044,13 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="C117" s="2">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2058,10 +2058,10 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>45997</v>
+        <v>46003</v>
       </c>
       <c r="C118" s="2">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>7</v>
@@ -2072,13 +2072,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="C119" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2089,7 +2089,7 @@
         <v>46005</v>
       </c>
       <c r="C120" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>7</v>
@@ -2103,10 +2103,10 @@
         <v>46005</v>
       </c>
       <c r="C121" s="2">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2114,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>46006</v>
+        <v>46005</v>
       </c>
       <c r="C122" s="2">
-        <v>356</v>
+        <v>54</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>46008</v>
+        <v>46006</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>7</v>
@@ -2142,13 +2142,13 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C124" s="2">
-        <v>489</v>
+        <v>46</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2156,13 +2156,13 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>46011</v>
+        <v>46008</v>
       </c>
       <c r="C125" s="2">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,13 +2170,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>46012</v>
+        <v>46009</v>
       </c>
       <c r="C126" s="2">
-        <v>1040</v>
+        <v>82</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2184,10 +2184,10 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C127" s="2">
-        <v>673</v>
+        <v>345</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>7</v>
@@ -2198,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C128" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>7</v>
@@ -2212,13 +2212,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C129" s="2">
-        <v>6</v>
+        <v>533</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2226,13 +2226,13 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>46014</v>
+        <v>46011</v>
       </c>
       <c r="C130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2240,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>46015</v>
+        <v>46012</v>
       </c>
       <c r="C131" s="2">
-        <v>1186</v>
+        <v>883</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2254,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>46015</v>
+        <v>46012</v>
       </c>
       <c r="C132" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>7</v>
@@ -2268,13 +2268,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>46016</v>
+        <v>46013</v>
       </c>
       <c r="C133" s="2">
-        <v>499</v>
+        <v>1279</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,13 +2282,13 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C134" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2296,10 +2296,10 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>46018</v>
+        <v>46014</v>
       </c>
       <c r="C135" s="2">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>7</v>
@@ -2310,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>46019</v>
+        <v>46015</v>
       </c>
       <c r="C136" s="2">
-        <v>465</v>
+        <v>604</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2324,13 +2324,13 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>46019</v>
+        <v>46016</v>
       </c>
       <c r="C137" s="2">
-        <v>777</v>
+        <v>1035</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>46020</v>
+        <v>46018</v>
       </c>
       <c r="C138" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>7</v>
@@ -2352,10 +2352,10 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>46021</v>
+        <v>46018</v>
       </c>
       <c r="C139" s="2">
-        <v>1</v>
+        <v>567</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>7</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>46021</v>
+        <v>46019</v>
       </c>
       <c r="C140" s="2">
-        <v>51</v>
+        <v>1514</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2380,13 +2380,13 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>46022</v>
+        <v>46020</v>
       </c>
       <c r="C141" s="2">
-        <v>607</v>
+        <v>1</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="C142" s="2">
-        <v>588</v>
+        <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>7</v>
@@ -2408,10 +2408,10 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C143" s="2">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>7</v>
@@ -2422,10 +2422,10 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>7</v>
@@ -2436,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
@@ -2450,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C146" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C147" s="2">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -2478,13 +2478,13 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>46025</v>
+        <v>46030</v>
       </c>
       <c r="C148" s="2">
-        <v>406</v>
+        <v>6</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2492,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>46025</v>
+        <v>46030</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2506,10 +2506,10 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>7</v>
@@ -2520,13 +2520,13 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>46026</v>
+        <v>46031</v>
       </c>
       <c r="C151" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2534,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>46028</v>
+        <v>46032</v>
       </c>
       <c r="C152" s="2">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>7</v>
@@ -2548,13 +2548,13 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>46028</v>
+        <v>46033</v>
       </c>
       <c r="C153" s="2">
-        <v>258</v>
+        <v>4</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2562,10 +2562,10 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>46029</v>
+        <v>46033</v>
       </c>
       <c r="C154" s="2">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>7</v>
@@ -2576,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C155" s="2">
         <v>7</v>
@@ -2590,13 +2590,13 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="C156" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,13 +2604,13 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>46032</v>
+        <v>45986</v>
       </c>
       <c r="C157" s="2">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2618,13 +2618,13 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>45974</v>
+        <v>45989</v>
       </c>
       <c r="C158" s="2">
+        <v>174</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>45983</v>
+        <v>45989</v>
       </c>
       <c r="C159" s="2">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2649,10 +2649,10 @@
         <v>45990</v>
       </c>
       <c r="C160" s="2">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2663,10 +2663,10 @@
         <v>45992</v>
       </c>
       <c r="C161" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2677,10 +2677,10 @@
         <v>45993</v>
       </c>
       <c r="C162" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="C163" s="2">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2702,13 +2702,13 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>45999</v>
+        <v>45994</v>
       </c>
       <c r="C164" s="2">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>46000</v>
+        <v>45995</v>
       </c>
       <c r="C165" s="2">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2730,10 +2730,10 @@
         <v>1</v>
       </c>
       <c r="B166" s="2">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="C166" s="2">
-        <v>5</v>
+        <v>411</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>7</v>
@@ -2744,10 +2744,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c r="C167" s="2">
-        <v>538</v>
+        <v>2</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>7</v>
@@ -2758,13 +2758,13 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>46004</v>
+        <v>45997</v>
       </c>
       <c r="C168" s="2">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2772,10 +2772,10 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>7</v>
@@ -2786,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>46005</v>
+        <v>45999</v>
       </c>
       <c r="C170" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>7</v>
@@ -2800,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="B171" s="2">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C171" s="2">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2814,10 +2814,10 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C172" s="2">
-        <v>382</v>
+        <v>321</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>7</v>
@@ -2828,13 +2828,13 @@
         <v>1</v>
       </c>
       <c r="B173" s="2">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C173" s="2">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2842,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>46008</v>
+        <v>46004</v>
       </c>
       <c r="C174" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
@@ -2856,10 +2856,10 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C175" s="2">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>7</v>
@@ -2870,13 +2870,13 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="C176" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2884,10 +2884,10 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="C177" s="2">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>7</v>
@@ -2898,10 +2898,10 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="C178" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>7</v>
@@ -2915,10 +2915,10 @@
         <v>46012</v>
       </c>
       <c r="C179" s="2">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2926,10 +2926,10 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C180" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>7</v>
@@ -2940,10 +2940,10 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C181" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>7</v>
@@ -2957,10 +2957,10 @@
         <v>46015</v>
       </c>
       <c r="C182" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2968,13 +2968,13 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="C183" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2982,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>46018</v>
+        <v>46015</v>
       </c>
       <c r="C184" s="2">
-        <v>4</v>
+        <v>311</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2996,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>46018</v>
+        <v>46016</v>
       </c>
       <c r="C185" s="2">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3010,13 +3010,13 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>46019</v>
+        <v>46017</v>
       </c>
       <c r="C186" s="2">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C187" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>7</v>
@@ -3038,10 +3038,10 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>46021</v>
+        <v>46017</v>
       </c>
       <c r="C188" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
@@ -3052,13 +3052,13 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C189" s="2">
-        <v>493</v>
+        <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3066,13 +3066,13 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>46022</v>
+        <v>46018</v>
       </c>
       <c r="C190" s="2">
-        <v>2030</v>
+        <v>273</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>46023</v>
+        <v>46019</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>46024</v>
+        <v>46019</v>
       </c>
       <c r="C192" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>7</v>
@@ -3108,10 +3108,10 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>46024</v>
+        <v>46019</v>
       </c>
       <c r="C193" s="2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>7</v>
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>7</v>
@@ -3136,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>46025</v>
+        <v>46020</v>
       </c>
       <c r="C195" s="2">
-        <v>310</v>
+        <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3150,10 +3150,10 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>46025</v>
+        <v>46021</v>
       </c>
       <c r="C196" s="2">
-        <v>1099</v>
+        <v>417</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>6</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>46027</v>
+        <v>46021</v>
       </c>
       <c r="C197" s="2">
-        <v>2</v>
+        <v>696</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3178,10 +3178,10 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>46027</v>
+        <v>46022</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>7</v>
@@ -3192,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>46028</v>
+        <v>46022</v>
       </c>
       <c r="C199" s="2">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>7</v>
@@ -3206,13 +3206,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="C200" s="2">
-        <v>1411</v>
+        <v>1</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3220,13 +3220,13 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="C201" s="2">
-        <v>460</v>
+        <v>608</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3234,13 +3234,13 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>46030</v>
+        <v>46024</v>
       </c>
       <c r="C202" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3248,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>46031</v>
+        <v>46025</v>
       </c>
       <c r="C203" s="2">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>7</v>
@@ -3262,10 +3262,10 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>46031</v>
+        <v>46025</v>
       </c>
       <c r="C204" s="2">
-        <v>2</v>
+        <v>1469</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>7</v>
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>46031</v>
+        <v>46025</v>
       </c>
       <c r="C205" s="2">
-        <v>837</v>
+        <v>72</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3290,13 +3290,13 @@
         <v>1</v>
       </c>
       <c r="B206" s="2">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="C206" s="2">
-        <v>9</v>
+        <v>906</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3304,10 +3304,10 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="C207" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -3318,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>46032</v>
+        <v>46026</v>
       </c>
       <c r="C208" s="2">
-        <v>2029</v>
+        <v>1</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>7</v>
@@ -3332,13 +3332,13 @@
         <v>1</v>
       </c>
       <c r="B209" s="2">
-        <v>45968</v>
+        <v>46027</v>
       </c>
       <c r="C209" s="2">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3346,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>45982</v>
+        <v>46028</v>
       </c>
       <c r="C210" s="2">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3360,10 +3360,10 @@
         <v>1</v>
       </c>
       <c r="B211" s="2">
-        <v>45989</v>
+        <v>46028</v>
       </c>
       <c r="C211" s="2">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -3374,13 +3374,13 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>45989</v>
+        <v>46029</v>
       </c>
       <c r="C212" s="2">
-        <v>1</v>
+        <v>1128</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3388,13 +3388,13 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>45990</v>
+        <v>46030</v>
       </c>
       <c r="C213" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3402,10 +3402,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>45991</v>
+        <v>46031</v>
       </c>
       <c r="C214" s="2">
-        <v>309</v>
+        <v>1354</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
@@ -3416,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>45991</v>
+        <v>46032</v>
       </c>
       <c r="C215" s="2">
-        <v>3</v>
+        <v>849</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3430,10 +3430,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="2">
-        <v>45992</v>
+        <v>46033</v>
       </c>
       <c r="C216" s="2">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>7</v>
@@ -3444,10 +3444,10 @@
         <v>1</v>
       </c>
       <c r="B217" s="2">
-        <v>45994</v>
+        <v>45968</v>
       </c>
       <c r="C217" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3458,13 +3458,13 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>45994</v>
+        <v>45982</v>
       </c>
       <c r="C218" s="2">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,10 +3472,10 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>45995</v>
+        <v>45989</v>
       </c>
       <c r="C219" s="2">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>7</v>
@@ -3486,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>45996</v>
+        <v>45989</v>
       </c>
       <c r="C220" s="2">
         <v>1</v>
@@ -3500,13 +3500,13 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>45997</v>
+        <v>45990</v>
       </c>
       <c r="C221" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3514,10 +3514,10 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>45997</v>
+        <v>45991</v>
       </c>
       <c r="C222" s="2">
-        <v>1156</v>
+        <v>309</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>7</v>
@@ -3528,10 +3528,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C223" s="2">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
@@ -3542,13 +3542,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>46000</v>
+        <v>45992</v>
       </c>
       <c r="C224" s="2">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3556,13 +3556,13 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>46001</v>
+        <v>45994</v>
       </c>
       <c r="C225" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3570,13 +3570,13 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="C226" s="2">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3584,13 +3584,13 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>46003</v>
+        <v>45995</v>
       </c>
       <c r="C227" s="2">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3598,13 +3598,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>46004</v>
+        <v>45996</v>
       </c>
       <c r="C228" s="2">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3612,13 +3612,13 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>46005</v>
+        <v>45997</v>
       </c>
       <c r="C229" s="2">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3626,10 +3626,10 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>46006</v>
+        <v>45997</v>
       </c>
       <c r="C230" s="2">
-        <v>1</v>
+        <v>1156</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>7</v>
@@ -3640,13 +3640,13 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>46008</v>
+        <v>45998</v>
       </c>
       <c r="C231" s="2">
-        <v>436</v>
+        <v>132</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3654,13 +3654,13 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>46009</v>
+        <v>46000</v>
       </c>
       <c r="C232" s="2">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3668,10 +3668,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C233" s="2">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>7</v>
@@ -3682,13 +3682,13 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>46011</v>
+        <v>46002</v>
       </c>
       <c r="C234" s="2">
-        <v>850</v>
+        <v>173</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3696,13 +3696,13 @@
         <v>1</v>
       </c>
       <c r="B235" s="2">
-        <v>46011</v>
+        <v>46003</v>
       </c>
       <c r="C235" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,13 +3710,13 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>46012</v>
+        <v>46004</v>
       </c>
       <c r="C236" s="2">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3724,13 +3724,13 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>46013</v>
+        <v>46005</v>
       </c>
       <c r="C237" s="2">
-        <v>5</v>
+        <v>330</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3738,13 +3738,13 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C238" s="2">
-        <v>270</v>
+        <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3752,13 +3752,13 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>46014</v>
+        <v>46008</v>
       </c>
       <c r="C239" s="2">
-        <v>39</v>
+        <v>436</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3766,10 +3766,10 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>46016</v>
+        <v>46009</v>
       </c>
       <c r="C240" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>7</v>
@@ -3780,10 +3780,10 @@
         <v>1</v>
       </c>
       <c r="B241" s="2">
-        <v>46017</v>
+        <v>46009</v>
       </c>
       <c r="C241" s="2">
-        <v>723</v>
+        <v>1</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>7</v>
@@ -3794,13 +3794,13 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>46017</v>
+        <v>46011</v>
       </c>
       <c r="C242" s="2">
-        <v>39</v>
+        <v>850</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3808,10 +3808,10 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>46019</v>
+        <v>46011</v>
       </c>
       <c r="C243" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="B244" s="2">
-        <v>46019</v>
+        <v>46012</v>
       </c>
       <c r="C244" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>7</v>
@@ -3836,10 +3836,10 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>46020</v>
+        <v>46013</v>
       </c>
       <c r="C245" s="2">
-        <v>575</v>
+        <v>5</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>7</v>
@@ -3850,13 +3850,13 @@
         <v>1</v>
       </c>
       <c r="B246" s="2">
-        <v>46020</v>
+        <v>46013</v>
       </c>
       <c r="C246" s="2">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3864,13 +3864,13 @@
         <v>1</v>
       </c>
       <c r="B247" s="2">
-        <v>46023</v>
+        <v>46014</v>
       </c>
       <c r="C247" s="2">
-        <v>528</v>
+        <v>39</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3878,10 +3878,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="2">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="C248" s="2">
-        <v>936</v>
+        <v>3</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>7</v>
@@ -3892,10 +3892,10 @@
         <v>1</v>
       </c>
       <c r="B249" s="2">
-        <v>46024</v>
+        <v>46017</v>
       </c>
       <c r="C249" s="2">
-        <v>89</v>
+        <v>723</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>7</v>
@@ -3906,10 +3906,10 @@
         <v>1</v>
       </c>
       <c r="B250" s="2">
-        <v>46024</v>
+        <v>46017</v>
       </c>
       <c r="C250" s="2">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>7</v>
@@ -3920,10 +3920,10 @@
         <v>1</v>
       </c>
       <c r="B251" s="2">
-        <v>46025</v>
+        <v>46019</v>
       </c>
       <c r="C251" s="2">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>7</v>
@@ -3934,13 +3934,13 @@
         <v>1</v>
       </c>
       <c r="B252" s="2">
-        <v>46026</v>
+        <v>46019</v>
       </c>
       <c r="C252" s="2">
-        <v>311</v>
+        <v>8</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3948,10 +3948,10 @@
         <v>1</v>
       </c>
       <c r="B253" s="2">
-        <v>46026</v>
+        <v>46020</v>
       </c>
       <c r="C253" s="2">
-        <v>969</v>
+        <v>575</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>7</v>
@@ -3962,10 +3962,10 @@
         <v>1</v>
       </c>
       <c r="B254" s="2">
-        <v>46027</v>
+        <v>46020</v>
       </c>
       <c r="C254" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>7</v>
@@ -3976,13 +3976,13 @@
         <v>1</v>
       </c>
       <c r="B255" s="2">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="C255" s="2">
-        <v>4</v>
+        <v>528</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3990,13 +3990,13 @@
         <v>1</v>
       </c>
       <c r="B256" s="2">
-        <v>46029</v>
+        <v>46023</v>
       </c>
       <c r="C256" s="2">
-        <v>183</v>
+        <v>936</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4004,13 +4004,13 @@
         <v>1</v>
       </c>
       <c r="B257" s="2">
-        <v>46029</v>
+        <v>46024</v>
       </c>
       <c r="C257" s="2">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4018,10 +4018,10 @@
         <v>1</v>
       </c>
       <c r="B258" s="2">
-        <v>46030</v>
+        <v>46024</v>
       </c>
       <c r="C258" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>7</v>
@@ -4032,10 +4032,10 @@
         <v>1</v>
       </c>
       <c r="B259" s="2">
-        <v>46032</v>
+        <v>46025</v>
       </c>
       <c r="C259" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>7</v>
@@ -4046,10 +4046,10 @@
         <v>1</v>
       </c>
       <c r="B260" s="2">
-        <v>46032</v>
+        <v>46026</v>
       </c>
       <c r="C260" s="2">
-        <v>130</v>
+        <v>311</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>5</v>
@@ -4060,13 +4060,13 @@
         <v>1</v>
       </c>
       <c r="B261" s="2">
-        <v>46032</v>
+        <v>46026</v>
       </c>
       <c r="C261" s="2">
-        <v>2</v>
+        <v>969</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4074,10 +4074,10 @@
         <v>1</v>
       </c>
       <c r="B262" s="2">
-        <v>46033</v>
+        <v>46027</v>
       </c>
       <c r="C262" s="2">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>7</v>
@@ -4088,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="B263" s="2">
-        <v>45982</v>
+        <v>46028</v>
       </c>
       <c r="C263" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4102,10 +4102,10 @@
         <v>1</v>
       </c>
       <c r="B264" s="2">
-        <v>45985</v>
+        <v>46029</v>
       </c>
       <c r="C264" s="2">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>5</v>
@@ -4116,13 +4116,13 @@
         <v>1</v>
       </c>
       <c r="B265" s="2">
-        <v>45986</v>
+        <v>46029</v>
       </c>
       <c r="C265" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4130,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="B266" s="2">
-        <v>45988</v>
+        <v>46030</v>
       </c>
       <c r="C266" s="2">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4144,10 +4144,10 @@
         <v>1</v>
       </c>
       <c r="B267" s="2">
-        <v>45989</v>
+        <v>46032</v>
       </c>
       <c r="C267" s="2">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>7</v>
@@ -4158,10 +4158,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="2">
-        <v>45991</v>
+        <v>46032</v>
       </c>
       <c r="C268" s="2">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>5</v>
@@ -4172,13 +4172,13 @@
         <v>1</v>
       </c>
       <c r="B269" s="2">
-        <v>45992</v>
+        <v>46032</v>
       </c>
       <c r="C269" s="2">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4186,10 +4186,10 @@
         <v>1</v>
       </c>
       <c r="B270" s="2">
-        <v>45993</v>
+        <v>46033</v>
       </c>
       <c r="C270" s="2">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>7</v>
@@ -4200,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="B271" s="2">
-        <v>45994</v>
+        <v>45966</v>
       </c>
       <c r="C271" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4214,13 +4214,13 @@
         <v>1</v>
       </c>
       <c r="B272" s="2">
-        <v>45995</v>
+        <v>45969</v>
       </c>
       <c r="C272" s="2">
-        <v>357</v>
+        <v>1</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4228,13 +4228,13 @@
         <v>1</v>
       </c>
       <c r="B273" s="2">
-        <v>45997</v>
+        <v>45985</v>
       </c>
       <c r="C273" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4242,13 +4242,13 @@
         <v>1</v>
       </c>
       <c r="B274" s="2">
-        <v>45997</v>
+        <v>45988</v>
       </c>
       <c r="C274" s="2">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4256,13 +4256,13 @@
         <v>1</v>
       </c>
       <c r="B275" s="2">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="C275" s="2">
-        <v>1061</v>
+        <v>113</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4270,13 +4270,13 @@
         <v>1</v>
       </c>
       <c r="B276" s="2">
-        <v>45998</v>
+        <v>45994</v>
       </c>
       <c r="C276" s="2">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4284,10 +4284,10 @@
         <v>1</v>
       </c>
       <c r="B277" s="2">
-        <v>46000</v>
+        <v>45996</v>
       </c>
       <c r="C277" s="2">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>7</v>
@@ -4298,10 +4298,10 @@
         <v>1</v>
       </c>
       <c r="B278" s="2">
-        <v>46001</v>
+        <v>45997</v>
       </c>
       <c r="C278" s="2">
-        <v>398</v>
+        <v>4</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>7</v>
@@ -4312,13 +4312,13 @@
         <v>1</v>
       </c>
       <c r="B279" s="2">
-        <v>46001</v>
+        <v>45997</v>
       </c>
       <c r="C279" s="2">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4326,13 +4326,13 @@
         <v>1</v>
       </c>
       <c r="B280" s="2">
-        <v>46003</v>
+        <v>45998</v>
       </c>
       <c r="C280" s="2">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4340,13 +4340,13 @@
         <v>1</v>
       </c>
       <c r="B281" s="2">
-        <v>46004</v>
+        <v>45998</v>
       </c>
       <c r="C281" s="2">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4354,13 +4354,13 @@
         <v>1</v>
       </c>
       <c r="B282" s="2">
-        <v>46004</v>
+        <v>45999</v>
       </c>
       <c r="C282" s="2">
-        <v>447</v>
+        <v>106</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4368,13 +4368,13 @@
         <v>1</v>
       </c>
       <c r="B283" s="2">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C283" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4382,10 +4382,10 @@
         <v>1</v>
       </c>
       <c r="B284" s="2">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C284" s="2">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>7</v>
@@ -4396,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="B285" s="2">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="C285" s="2">
         <v>2</v>
@@ -4410,13 +4410,13 @@
         <v>1</v>
       </c>
       <c r="B286" s="2">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="C286" s="2">
-        <v>436</v>
+        <v>76</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4424,10 +4424,10 @@
         <v>1</v>
       </c>
       <c r="B287" s="2">
-        <v>46010</v>
+        <v>46005</v>
       </c>
       <c r="C287" s="2">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>7</v>
@@ -4438,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="B288" s="2">
-        <v>46010</v>
+        <v>46005</v>
       </c>
       <c r="C288" s="2">
-        <v>5</v>
+        <v>926</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>7</v>
@@ -4452,13 +4452,13 @@
         <v>1</v>
       </c>
       <c r="B289" s="2">
-        <v>46011</v>
+        <v>46007</v>
       </c>
       <c r="C289" s="2">
-        <v>267</v>
+        <v>33</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4466,13 +4466,13 @@
         <v>1</v>
       </c>
       <c r="B290" s="2">
-        <v>46011</v>
+        <v>46007</v>
       </c>
       <c r="C290" s="2">
-        <v>234</v>
+        <v>36</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4480,10 +4480,10 @@
         <v>1</v>
       </c>
       <c r="B291" s="2">
-        <v>46012</v>
+        <v>46008</v>
       </c>
       <c r="C291" s="2">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>7</v>
@@ -4494,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="B292" s="2">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C292" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4508,10 +4508,10 @@
         <v>1</v>
       </c>
       <c r="B293" s="2">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C293" s="2">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>7</v>
@@ -4522,10 +4522,10 @@
         <v>1</v>
       </c>
       <c r="B294" s="2">
-        <v>46014</v>
+        <v>46011</v>
       </c>
       <c r="C294" s="2">
-        <v>6</v>
+        <v>1006</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>7</v>
@@ -4536,13 +4536,13 @@
         <v>1</v>
       </c>
       <c r="B295" s="2">
-        <v>46014</v>
+        <v>46012</v>
       </c>
       <c r="C295" s="2">
-        <v>321</v>
+        <v>2</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4550,13 +4550,13 @@
         <v>1</v>
       </c>
       <c r="B296" s="2">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="C296" s="2">
-        <v>393</v>
+        <v>38</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4564,10 +4564,10 @@
         <v>1</v>
       </c>
       <c r="B297" s="2">
-        <v>46015</v>
+        <v>46014</v>
       </c>
       <c r="C297" s="2">
-        <v>62</v>
+        <v>767</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>7</v>
@@ -4578,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="B298" s="2">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="C298" s="2">
-        <v>1</v>
+        <v>1313</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="B299" s="2">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="C299" s="2">
         <v>3</v>
@@ -4606,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="B300" s="2">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="C300" s="2">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4620,13 +4620,13 @@
         <v>1</v>
       </c>
       <c r="B301" s="2">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="C301" s="2">
-        <v>246</v>
+        <v>18</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4634,13 +4634,13 @@
         <v>1</v>
       </c>
       <c r="B302" s="2">
-        <v>46018</v>
+        <v>46017</v>
       </c>
       <c r="C302" s="2">
-        <v>54</v>
+        <v>1018</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4648,10 +4648,10 @@
         <v>1</v>
       </c>
       <c r="B303" s="2">
-        <v>46019</v>
+        <v>46018</v>
       </c>
       <c r="C303" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>7</v>
@@ -4665,10 +4665,10 @@
         <v>46020</v>
       </c>
       <c r="C304" s="2">
-        <v>628</v>
+        <v>5</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4679,10 +4679,10 @@
         <v>46020</v>
       </c>
       <c r="C305" s="2">
-        <v>3</v>
+        <v>2045</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4690,10 +4690,10 @@
         <v>1</v>
       </c>
       <c r="B306" s="2">
-        <v>46021</v>
+        <v>46023</v>
       </c>
       <c r="C306" s="2">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>7</v>
@@ -4704,13 +4704,13 @@
         <v>1</v>
       </c>
       <c r="B307" s="2">
-        <v>46021</v>
+        <v>46023</v>
       </c>
       <c r="C307" s="2">
-        <v>612</v>
+        <v>1552</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4718,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="B308" s="2">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="C308" s="2">
         <v>1</v>
@@ -4735,7 +4735,7 @@
         <v>46023</v>
       </c>
       <c r="C309" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>7</v>
@@ -4746,13 +4746,13 @@
         <v>1</v>
       </c>
       <c r="B310" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C310" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4760,10 +4760,10 @@
         <v>1</v>
       </c>
       <c r="B311" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C311" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>7</v>
@@ -4774,10 +4774,10 @@
         <v>1</v>
       </c>
       <c r="B312" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C312" s="2">
-        <v>1445</v>
+        <v>13</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>7</v>
@@ -4788,13 +4788,13 @@
         <v>1</v>
       </c>
       <c r="B313" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C313" s="2">
-        <v>1</v>
+        <v>322</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4802,10 +4802,10 @@
         <v>1</v>
       </c>
       <c r="B314" s="2">
-        <v>46026</v>
+        <v>46028</v>
       </c>
       <c r="C314" s="2">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>7</v>
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="B315" s="2">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C315" s="2">
-        <v>565</v>
+        <v>1</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>7</v>
@@ -4833,7 +4833,7 @@
         <v>46029</v>
       </c>
       <c r="C316" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>7</v>
@@ -4847,7 +4847,7 @@
         <v>46029</v>
       </c>
       <c r="C317" s="2">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>7</v>
@@ -4861,7 +4861,7 @@
         <v>46030</v>
       </c>
       <c r="C318" s="2">
-        <v>667</v>
+        <v>7</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>7</v>
@@ -4875,10 +4875,10 @@
         <v>46030</v>
       </c>
       <c r="C319" s="2">
-        <v>976</v>
+        <v>138</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4886,10 +4886,10 @@
         <v>1</v>
       </c>
       <c r="B320" s="2">
-        <v>46032</v>
+        <v>46031</v>
       </c>
       <c r="C320" s="2">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>7</v>
@@ -4900,13 +4900,13 @@
         <v>1</v>
       </c>
       <c r="B321" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C321" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4914,13 +4914,13 @@
         <v>1</v>
       </c>
       <c r="B322" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C322" s="2">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4928,13 +4928,13 @@
         <v>1</v>
       </c>
       <c r="B323" s="2">
-        <v>46033</v>
+        <v>45981</v>
       </c>
       <c r="C323" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4942,13 +4942,13 @@
         <v>1</v>
       </c>
       <c r="B324" s="2">
-        <v>46033</v>
+        <v>45984</v>
       </c>
       <c r="C324" s="2">
-        <v>533</v>
+        <v>36</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4956,13 +4956,13 @@
         <v>1</v>
       </c>
       <c r="B325" s="2">
-        <v>46033</v>
+        <v>45987</v>
       </c>
       <c r="C325" s="2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4970,13 +4970,13 @@
         <v>1</v>
       </c>
       <c r="B326" s="2">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="C326" s="2">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4984,13 +4984,13 @@
         <v>1</v>
       </c>
       <c r="B327" s="2">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C327" s="2">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4998,13 +4998,13 @@
         <v>1</v>
       </c>
       <c r="B328" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="C328" s="2">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5012,13 +5012,13 @@
         <v>1</v>
       </c>
       <c r="B329" s="2">
-        <v>45990</v>
+        <v>45995</v>
       </c>
       <c r="C329" s="2">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5026,13 +5026,13 @@
         <v>1</v>
       </c>
       <c r="B330" s="2">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C330" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5040,10 +5040,10 @@
         <v>1</v>
       </c>
       <c r="B331" s="2">
-        <v>45993</v>
+        <v>45996</v>
       </c>
       <c r="C331" s="2">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>7</v>
@@ -5054,13 +5054,13 @@
         <v>1</v>
       </c>
       <c r="B332" s="2">
-        <v>45993</v>
+        <v>45997</v>
       </c>
       <c r="C332" s="2">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5068,13 +5068,13 @@
         <v>1</v>
       </c>
       <c r="B333" s="2">
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="C333" s="2">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5082,13 +5082,13 @@
         <v>1</v>
       </c>
       <c r="B334" s="2">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="C334" s="2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5096,10 +5096,10 @@
         <v>1</v>
       </c>
       <c r="B335" s="2">
-        <v>45996</v>
+        <v>46004</v>
       </c>
       <c r="C335" s="2">
-        <v>411</v>
+        <v>1130</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>7</v>
@@ -5110,10 +5110,10 @@
         <v>1</v>
       </c>
       <c r="B336" s="2">
-        <v>45996</v>
+        <v>46004</v>
       </c>
       <c r="C336" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>7</v>
@@ -5124,13 +5124,13 @@
         <v>1</v>
       </c>
       <c r="B337" s="2">
-        <v>45997</v>
+        <v>46007</v>
       </c>
       <c r="C337" s="2">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5138,10 +5138,10 @@
         <v>1</v>
       </c>
       <c r="B338" s="2">
-        <v>45999</v>
+        <v>46008</v>
       </c>
       <c r="C338" s="2">
-        <v>358</v>
+        <v>64</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>7</v>
@@ -5152,13 +5152,13 @@
         <v>1</v>
       </c>
       <c r="B339" s="2">
-        <v>45999</v>
+        <v>46010</v>
       </c>
       <c r="C339" s="2">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5166,13 +5166,13 @@
         <v>1</v>
       </c>
       <c r="B340" s="2">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="C340" s="2">
-        <v>133</v>
+        <v>558</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5180,10 +5180,10 @@
         <v>1</v>
       </c>
       <c r="B341" s="2">
-        <v>46002</v>
+        <v>46011</v>
       </c>
       <c r="C341" s="2">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>7</v>
@@ -5194,13 +5194,13 @@
         <v>1</v>
       </c>
       <c r="B342" s="2">
-        <v>46003</v>
+        <v>46012</v>
       </c>
       <c r="C342" s="2">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5208,13 +5208,13 @@
         <v>1</v>
       </c>
       <c r="B343" s="2">
-        <v>46004</v>
+        <v>46013</v>
       </c>
       <c r="C343" s="2">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5222,13 +5222,13 @@
         <v>1</v>
       </c>
       <c r="B344" s="2">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="C344" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5236,10 +5236,10 @@
         <v>1</v>
       </c>
       <c r="B345" s="2">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C345" s="2">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>7</v>
@@ -5250,10 +5250,10 @@
         <v>1</v>
       </c>
       <c r="B346" s="2">
-        <v>46011</v>
+        <v>46016</v>
       </c>
       <c r="C346" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>7</v>
@@ -5264,13 +5264,13 @@
         <v>1</v>
       </c>
       <c r="B347" s="2">
-        <v>46011</v>
+        <v>46016</v>
       </c>
       <c r="C347" s="2">
-        <v>12</v>
+        <v>233</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5278,13 +5278,13 @@
         <v>1</v>
       </c>
       <c r="B348" s="2">
-        <v>46012</v>
+        <v>46016</v>
       </c>
       <c r="C348" s="2">
-        <v>349</v>
+        <v>3</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5292,10 +5292,10 @@
         <v>1</v>
       </c>
       <c r="B349" s="2">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="C349" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>7</v>
@@ -5306,13 +5306,13 @@
         <v>1</v>
       </c>
       <c r="B350" s="2">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="C350" s="2">
-        <v>16</v>
+        <v>1017</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5320,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="B351" s="2">
-        <v>46015</v>
+        <v>46019</v>
       </c>
       <c r="C351" s="2">
         <v>6</v>
@@ -5334,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="B352" s="2">
-        <v>46015</v>
+        <v>46019</v>
       </c>
       <c r="C352" s="2">
         <v>2</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5348,13 +5348,13 @@
         <v>1</v>
       </c>
       <c r="B353" s="2">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C353" s="2">
-        <v>311</v>
+        <v>4</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5362,13 +5362,13 @@
         <v>1</v>
       </c>
       <c r="B354" s="2">
-        <v>46016</v>
+        <v>46020</v>
       </c>
       <c r="C354" s="2">
-        <v>45</v>
+        <v>486</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5376,13 +5376,13 @@
         <v>1</v>
       </c>
       <c r="B355" s="2">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="C355" s="2">
-        <v>1</v>
+        <v>2287</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5390,10 +5390,10 @@
         <v>1</v>
       </c>
       <c r="B356" s="2">
-        <v>46017</v>
+        <v>46023</v>
       </c>
       <c r="C356" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>7</v>
@@ -5404,13 +5404,13 @@
         <v>1</v>
       </c>
       <c r="B357" s="2">
-        <v>46017</v>
+        <v>46023</v>
       </c>
       <c r="C357" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5418,13 +5418,13 @@
         <v>1</v>
       </c>
       <c r="B358" s="2">
-        <v>46018</v>
+        <v>46024</v>
       </c>
       <c r="C358" s="2">
-        <v>1</v>
+        <v>1455</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5432,13 +5432,13 @@
         <v>1</v>
       </c>
       <c r="B359" s="2">
-        <v>46018</v>
+        <v>46025</v>
       </c>
       <c r="C359" s="2">
-        <v>273</v>
+        <v>27</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5446,10 +5446,10 @@
         <v>1</v>
       </c>
       <c r="B360" s="2">
-        <v>46019</v>
+        <v>46025</v>
       </c>
       <c r="C360" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>7</v>
@@ -5460,10 +5460,10 @@
         <v>1</v>
       </c>
       <c r="B361" s="2">
-        <v>46019</v>
+        <v>46025</v>
       </c>
       <c r="C361" s="2">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>7</v>
@@ -5474,10 +5474,10 @@
         <v>1</v>
       </c>
       <c r="B362" s="2">
-        <v>46019</v>
+        <v>46026</v>
       </c>
       <c r="C362" s="2">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>7</v>
@@ -5488,10 +5488,10 @@
         <v>1</v>
       </c>
       <c r="B363" s="2">
-        <v>46020</v>
+        <v>46026</v>
       </c>
       <c r="C363" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>7</v>
@@ -5502,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="B364" s="2">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="C364" s="2">
         <v>1</v>
@@ -5516,10 +5516,10 @@
         <v>1</v>
       </c>
       <c r="B365" s="2">
-        <v>46021</v>
+        <v>46027</v>
       </c>
       <c r="C365" s="2">
-        <v>417</v>
+        <v>1403</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>8</v>
@@ -5530,13 +5530,13 @@
         <v>1</v>
       </c>
       <c r="B366" s="2">
-        <v>46021</v>
+        <v>46027</v>
       </c>
       <c r="C366" s="2">
-        <v>696</v>
+        <v>48</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5544,10 +5544,10 @@
         <v>1</v>
       </c>
       <c r="B367" s="2">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="C367" s="2">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>7</v>
@@ -5558,10 +5558,10 @@
         <v>1</v>
       </c>
       <c r="B368" s="2">
-        <v>46022</v>
+        <v>46028</v>
       </c>
       <c r="C368" s="2">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>7</v>
@@ -5572,10 +5572,10 @@
         <v>1</v>
       </c>
       <c r="B369" s="2">
-        <v>46023</v>
+        <v>46029</v>
       </c>
       <c r="C369" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>7</v>
@@ -5586,13 +5586,13 @@
         <v>1</v>
       </c>
       <c r="B370" s="2">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="C370" s="2">
-        <v>608</v>
+        <v>32</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5600,13 +5600,13 @@
         <v>1</v>
       </c>
       <c r="B371" s="2">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C371" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5614,10 +5614,10 @@
         <v>1</v>
       </c>
       <c r="B372" s="2">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C372" s="2">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>7</v>
@@ -5628,10 +5628,10 @@
         <v>1</v>
       </c>
       <c r="B373" s="2">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="C373" s="2">
-        <v>1469</v>
+        <v>4</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>7</v>
@@ -5642,10 +5642,10 @@
         <v>1</v>
       </c>
       <c r="B374" s="2">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="C374" s="2">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>7</v>
@@ -5656,13 +5656,13 @@
         <v>1</v>
       </c>
       <c r="B375" s="2">
-        <v>46026</v>
+        <v>46033</v>
       </c>
       <c r="C375" s="2">
-        <v>906</v>
+        <v>1375</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5670,10 +5670,10 @@
         <v>1</v>
       </c>
       <c r="B376" s="2">
-        <v>46026</v>
+        <v>46033</v>
       </c>
       <c r="C376" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>7</v>
@@ -5684,13 +5684,13 @@
         <v>1</v>
       </c>
       <c r="B377" s="2">
-        <v>46026</v>
+        <v>45982</v>
       </c>
       <c r="C377" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5698,13 +5698,13 @@
         <v>1</v>
       </c>
       <c r="B378" s="2">
-        <v>46027</v>
+        <v>45985</v>
       </c>
       <c r="C378" s="2">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5712,10 +5712,10 @@
         <v>1</v>
       </c>
       <c r="B379" s="2">
-        <v>46028</v>
+        <v>45986</v>
       </c>
       <c r="C379" s="2">
-        <v>568</v>
+        <v>1</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>7</v>
@@ -5726,13 +5726,13 @@
         <v>1</v>
       </c>
       <c r="B380" s="2">
-        <v>46028</v>
+        <v>45988</v>
       </c>
       <c r="C380" s="2">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5740,13 +5740,13 @@
         <v>1</v>
       </c>
       <c r="B381" s="2">
-        <v>46029</v>
+        <v>45989</v>
       </c>
       <c r="C381" s="2">
-        <v>1128</v>
+        <v>57</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5754,13 +5754,13 @@
         <v>1</v>
       </c>
       <c r="B382" s="2">
-        <v>46030</v>
+        <v>45991</v>
       </c>
       <c r="C382" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5768,10 +5768,10 @@
         <v>1</v>
       </c>
       <c r="B383" s="2">
-        <v>46031</v>
+        <v>45992</v>
       </c>
       <c r="C383" s="2">
-        <v>1354</v>
+        <v>200</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>7</v>
@@ -5782,13 +5782,13 @@
         <v>1</v>
       </c>
       <c r="B384" s="2">
-        <v>46032</v>
+        <v>45993</v>
       </c>
       <c r="C384" s="2">
-        <v>849</v>
+        <v>1</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5796,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="B385" s="2">
-        <v>46033</v>
+        <v>45994</v>
       </c>
       <c r="C385" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D385" s="2" t="s">
         <v>7</v>
@@ -5810,13 +5810,13 @@
         <v>1</v>
       </c>
       <c r="B386" s="2">
-        <v>45981</v>
+        <v>45995</v>
       </c>
       <c r="C386" s="2">
-        <v>3</v>
+        <v>357</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5824,13 +5824,13 @@
         <v>1</v>
       </c>
       <c r="B387" s="2">
-        <v>45984</v>
+        <v>45997</v>
       </c>
       <c r="C387" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5838,13 +5838,13 @@
         <v>1</v>
       </c>
       <c r="B388" s="2">
-        <v>45987</v>
+        <v>45997</v>
       </c>
       <c r="C388" s="2">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5852,13 +5852,13 @@
         <v>1</v>
       </c>
       <c r="B389" s="2">
-        <v>45989</v>
+        <v>45998</v>
       </c>
       <c r="C389" s="2">
-        <v>179</v>
+        <v>1061</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5866,10 +5866,10 @@
         <v>1</v>
       </c>
       <c r="B390" s="2">
-        <v>45991</v>
+        <v>45998</v>
       </c>
       <c r="C390" s="2">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>8</v>
@@ -5880,13 +5880,13 @@
         <v>1</v>
       </c>
       <c r="B391" s="2">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="C391" s="2">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5894,13 +5894,13 @@
         <v>1</v>
       </c>
       <c r="B392" s="2">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="C392" s="2">
-        <v>72</v>
+        <v>398</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5908,13 +5908,13 @@
         <v>1</v>
       </c>
       <c r="B393" s="2">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="C393" s="2">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5922,10 +5922,10 @@
         <v>1</v>
       </c>
       <c r="B394" s="2">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="C394" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>7</v>
@@ -5936,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="B395" s="2">
-        <v>45997</v>
+        <v>46004</v>
       </c>
       <c r="C395" s="2">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5950,13 +5950,13 @@
         <v>1</v>
       </c>
       <c r="B396" s="2">
-        <v>45998</v>
+        <v>46004</v>
       </c>
       <c r="C396" s="2">
-        <v>15</v>
+        <v>447</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5964,10 +5964,10 @@
         <v>1</v>
       </c>
       <c r="B397" s="2">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="C397" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>7</v>
@@ -5978,10 +5978,10 @@
         <v>1</v>
       </c>
       <c r="B398" s="2">
-        <v>46004</v>
+        <v>46007</v>
       </c>
       <c r="C398" s="2">
-        <v>1130</v>
+        <v>4</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>7</v>
@@ -5992,10 +5992,10 @@
         <v>1</v>
       </c>
       <c r="B399" s="2">
-        <v>46004</v>
+        <v>46007</v>
       </c>
       <c r="C399" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>7</v>
@@ -6009,10 +6009,10 @@
         <v>46007</v>
       </c>
       <c r="C400" s="2">
-        <v>278</v>
+        <v>436</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6020,10 +6020,10 @@
         <v>1</v>
       </c>
       <c r="B401" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C401" s="2">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D401" s="2" t="s">
         <v>7</v>
@@ -6037,10 +6037,10 @@
         <v>46010</v>
       </c>
       <c r="C402" s="2">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6048,13 +6048,13 @@
         <v>1</v>
       </c>
       <c r="B403" s="2">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="C403" s="2">
-        <v>558</v>
+        <v>267</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6065,10 +6065,10 @@
         <v>46011</v>
       </c>
       <c r="C404" s="2">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6079,7 +6079,7 @@
         <v>46012</v>
       </c>
       <c r="C405" s="2">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="D405" s="2" t="s">
         <v>7</v>
@@ -6093,10 +6093,10 @@
         <v>46013</v>
       </c>
       <c r="C406" s="2">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6107,10 +6107,10 @@
         <v>46013</v>
       </c>
       <c r="C407" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6121,7 +6121,7 @@
         <v>46014</v>
       </c>
       <c r="C408" s="2">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="D408" s="2" t="s">
         <v>7</v>
@@ -6132,13 +6132,13 @@
         <v>1</v>
       </c>
       <c r="B409" s="2">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="C409" s="2">
-        <v>8</v>
+        <v>321</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6146,10 +6146,10 @@
         <v>1</v>
       </c>
       <c r="B410" s="2">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="C410" s="2">
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>5</v>
@@ -6160,10 +6160,10 @@
         <v>1</v>
       </c>
       <c r="B411" s="2">
-        <v>46016</v>
+        <v>46015</v>
       </c>
       <c r="C411" s="2">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D411" s="2" t="s">
         <v>7</v>
@@ -6174,10 +6174,10 @@
         <v>1</v>
       </c>
       <c r="B412" s="2">
-        <v>46017</v>
+        <v>46016</v>
       </c>
       <c r="C412" s="2">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>7</v>
@@ -6188,13 +6188,13 @@
         <v>1</v>
       </c>
       <c r="B413" s="2">
-        <v>46018</v>
+        <v>46017</v>
       </c>
       <c r="C413" s="2">
-        <v>1017</v>
+        <v>3</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6202,13 +6202,13 @@
         <v>1</v>
       </c>
       <c r="B414" s="2">
-        <v>46019</v>
+        <v>46017</v>
       </c>
       <c r="C414" s="2">
+        <v>-3</v>
+      </c>
+      <c r="D414" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D414" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6216,13 +6216,13 @@
         <v>1</v>
       </c>
       <c r="B415" s="2">
-        <v>46019</v>
+        <v>46017</v>
       </c>
       <c r="C415" s="2">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6230,10 +6230,10 @@
         <v>1</v>
       </c>
       <c r="B416" s="2">
-        <v>46020</v>
+        <v>46018</v>
       </c>
       <c r="C416" s="2">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="D416" s="2" t="s">
         <v>7</v>
@@ -6244,13 +6244,13 @@
         <v>1</v>
       </c>
       <c r="B417" s="2">
-        <v>46020</v>
+        <v>46019</v>
       </c>
       <c r="C417" s="2">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6258,13 +6258,13 @@
         <v>1</v>
       </c>
       <c r="B418" s="2">
-        <v>46021</v>
+        <v>46020</v>
       </c>
       <c r="C418" s="2">
-        <v>2287</v>
+        <v>628</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6272,13 +6272,13 @@
         <v>1</v>
       </c>
       <c r="B419" s="2">
-        <v>46023</v>
+        <v>46020</v>
       </c>
       <c r="C419" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6286,13 +6286,13 @@
         <v>1</v>
       </c>
       <c r="B420" s="2">
-        <v>46023</v>
+        <v>46021</v>
       </c>
       <c r="C420" s="2">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6300,13 +6300,13 @@
         <v>1</v>
       </c>
       <c r="B421" s="2">
-        <v>46024</v>
+        <v>46021</v>
       </c>
       <c r="C421" s="2">
-        <v>1455</v>
+        <v>612</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6314,10 +6314,10 @@
         <v>1</v>
       </c>
       <c r="B422" s="2">
-        <v>46025</v>
+        <v>46022</v>
       </c>
       <c r="C422" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>7</v>
@@ -6328,10 +6328,10 @@
         <v>1</v>
       </c>
       <c r="B423" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C423" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D423" s="2" t="s">
         <v>7</v>
@@ -6342,13 +6342,13 @@
         <v>1</v>
       </c>
       <c r="B424" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C424" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6356,10 +6356,10 @@
         <v>1</v>
       </c>
       <c r="B425" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C425" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D425" s="2" t="s">
         <v>7</v>
@@ -6370,10 +6370,10 @@
         <v>1</v>
       </c>
       <c r="B426" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C426" s="2">
-        <v>6</v>
+        <v>1445</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>7</v>
@@ -6384,7 +6384,7 @@
         <v>1</v>
       </c>
       <c r="B427" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C427" s="2">
         <v>1</v>
@@ -6398,13 +6398,13 @@
         <v>1</v>
       </c>
       <c r="B428" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C428" s="2">
-        <v>1403</v>
+        <v>30</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6415,7 +6415,7 @@
         <v>46027</v>
       </c>
       <c r="C429" s="2">
-        <v>48</v>
+        <v>565</v>
       </c>
       <c r="D429" s="2" t="s">
         <v>7</v>
@@ -6426,10 +6426,10 @@
         <v>1</v>
       </c>
       <c r="B430" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="C430" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D430" s="2" t="s">
         <v>7</v>
@@ -6440,10 +6440,10 @@
         <v>1</v>
       </c>
       <c r="B431" s="2">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="C431" s="2">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D431" s="2" t="s">
         <v>7</v>
@@ -6454,10 +6454,10 @@
         <v>1</v>
       </c>
       <c r="B432" s="2">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="C432" s="2">
-        <v>6</v>
+        <v>667</v>
       </c>
       <c r="D432" s="2" t="s">
         <v>7</v>
@@ -6471,10 +6471,10 @@
         <v>46030</v>
       </c>
       <c r="C433" s="2">
-        <v>32</v>
+        <v>976</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6482,10 +6482,10 @@
         <v>1</v>
       </c>
       <c r="B434" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C434" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>7</v>
@@ -6496,10 +6496,10 @@
         <v>1</v>
       </c>
       <c r="B435" s="2">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C435" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>7</v>
@@ -6513,7 +6513,7 @@
         <v>46032</v>
       </c>
       <c r="C436" s="2">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D436" s="2" t="s">
         <v>7</v>
@@ -6524,10 +6524,10 @@
         <v>1</v>
       </c>
       <c r="B437" s="2">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C437" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>7</v>
@@ -6541,10 +6541,10 @@
         <v>46033</v>
       </c>
       <c r="C438" s="2">
-        <v>1375</v>
+        <v>533</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6555,7 +6555,7 @@
         <v>46033</v>
       </c>
       <c r="C439" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>7</v>
